--- a/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
+++ b/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
@@ -35,7 +35,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +45,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F4858"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDECEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +79,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -554,12 +546,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>o03</t>
+          <t>o04</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Опорный пункт</t>
+          <t>Жила</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -569,104 +561,104 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ</t>
+          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Хотя бы одна из этих вышек стоит на гексе, где есть жетоны противника</t>
+          <t>Оба примыкают к нестартовым тайлам зарождения</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>6 монет, 1 трофей</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1 карта арсенала</t>
+          <t>attack модуль</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце [reaction kind=barrage]</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
+          <t>В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ, — награда 6 боеприпасов и 1 трофей. Если хотя бы одна из этих вышек стоит на гексе, где есть жетоны противника, условие усилено: 1 карта арсенала. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
+          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения, — награда 6 монет и 1 трофей. Если оба примыкают к нестартовым тайлам зарождения, условие усилено: жетон модуля атаки. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>o07</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Засада</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Держи так сразу два своих войска</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>6 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1 карта арсенала</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника, — награда 6 боеприпасов и 1 трофей. Держи так сразу два войска, и условие усилено: 1 карта арсенала. Гарнизон в здании не виден до первого выстрела.</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>o05</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Выработка</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>incident</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Этим ты полностью исчерпал зарождение, и тайл ушёл с поля</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>6 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>assembly модуль</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс [reaction kind=withdraw]</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения — награда 6 монет и 1 трофей. Если ты этим полностью исчерпал зарождение и тайл ушёл с поля, условие усилено: жетон модуля сборки. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
         </is>
       </c>
     </row>
@@ -676,27 +668,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>o11</t>
+          <t>o40</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Передовая база</t>
+          <t>Ва-банк</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>incident</t>
+          <t>state</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника</t>
+          <t>Имей одновременно ноль монет и ноль боеприпасов</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй его на гексе, соседнем с гексом, где есть здание противника</t>
+          <t>Обнули заодно и келемий</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -706,89 +698,89 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1 карта арсенала</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда 4 монеты и 1 трофей. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 карта арсенала. Передовая база строится под огнём — потому и платит.</t>
+          <t>Имей одновременно ноль монет и ноль боеприпасов — награда 4 монеты и 1 трофей. Обнули заодно и келемий, и условие усилено: 2 трофея. Ва-банк играют только на голом столе.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>o12</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Наглая стройка</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>o08</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Разведка недр</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД сделай это на гексе, где стоят два войска противника</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1 карта арсенала</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ РЫНОК [free_action action=market]</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника, — награда 8 монет и 1 трофей. Сделай это на гексе, где стоят два войска противника, и условие усилено: 1 карта арсенала. Стройка под чужим стволом — заявка, а не расчёт.</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД забери три контейнера — добытчиками или войсками</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>4 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД забери три контейнера — добытчиками или войсками, — награда 4 монеты и 1 трофей. Усиления у карты нет: три контейнера за ход и так работа всей смены. Каждый добытчик в Добыче выбирает одно: келемий или контейнер.</t>
         </is>
       </c>
     </row>
@@ -798,119 +790,119 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>o17</t>
+          <t>o01</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Штаб на передовой</t>
+          <t>Полный залп</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Имей своё военное здание на расстоянии не больше 2 гексов от гекса с ЦУ противника</t>
+          <t>В ЭТОТ ХОД произведи только боеприпасы и ни одного войска</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Это здание примыкает к гексу с ЦУ противника</t>
+          <t>Среди этих зданий есть и завод, и авиабаза</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>1 трофей, 2 карт задания</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>1 карта арсенала</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) [exchange_science_or_market amount=1]</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Имей своё военное здание — казарму, завод или авиабазу — на расстоянии не больше 2 гексов от гекса с ЦУ противника, — награда 6 монет и 1 трофей. Если это здание примыкает к гексу с чужим ЦУ, условие усилено: 4 трофея. Производство под самым носом врага экономит каждое перемещение — и первым попадает под удар.</t>
+          <t>В ЭТОТ ХОД произведи только боеприпасы и ни одного войска — награда 1 трофей и 2 карты задания. Если среди этих зданий есть и завод, и авиабаза, условие усилено: 1 карта арсенала. Ход без единого нового войска — цена полного залпа.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>o21</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Первая кровь</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>incident</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь два жетона противника</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД у одного из уничтоженных прочность была 2 или больше</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>attack модуль</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь два жетона противника — награда 8 монет и 1 трофей. Если у одного из них прочность была 2 или больше, условие усилено: жетон модуля атаки. Первая кровь считается по двум, а не по одному.</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>o29</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Пустой двор</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Имей два своих войска на гексах, где нет твоих зданий</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Четыре войска, и все стоят на разных гексах</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>assembly модуль</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце [reaction kind=return_fire]</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Имей два своих войска на гексах, где нет твоих зданий, — награда 1 трофей и 2 карты задания. Если таких войск четыре и все стоят на разных гексах, условие усилено: жетон модуля сборки. Войско без своего здания рядом умрёт первым — зато не даром.</t>
         </is>
       </c>
     </row>
@@ -920,123 +912,119 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>o22</t>
+          <t>o03</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Зачистка</t>
+          <t>Опорный пункт</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>sacrifice</t>
+          <t>state</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов здание противника и верни его владельцу</t>
+          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Хотя бы одна из этих вышек стоит на гексе, где есть жетоны противника</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>6 БПР, 1 трофей</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>assembly модуль</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>платит: 1 trophies</t>
-        </is>
-      </c>
+          <t>4 трофей</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце [reaction kind=return_fire]</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов здание противника и верни его владельцу — награда 6 монет и 1 трофей. Верни владельцу ещё один уничтоженный жетон, и условие усилено: жетон модуля сборки. Отданный уничтоженный жетон очков не приносит: за это и платят.</t>
+          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ, — награда 6 боеприпасов и 1 трофей. Если хотя бы одна из этих вышек стоит на гексе, где есть жетоны противника, условие усилено: 4 трофея. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>o25</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Осада</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>o07</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Засада</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Имей среди уничтоженных жетонов здание противника</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Среди твоих трофеев есть добытчик противника</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>attack модуль</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Имей среди уничтоженных жетонов здание противника — награда 2 монеты и 1 трофей. Если среди твоих трофеев есть добытчик противника, условие усилено: жетон модуля атаки. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Держи так сразу два своих войска</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>6 БПР, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>1 карта арсенала</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце [reaction kind=barrage]</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника, — награда 6 боеприпасов и 1 трофей. Держи так сразу два войска, и условие усилено: 1 карта арсенала. Гарнизон в здании не виден до первого выстрела.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1070,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
+          <t>РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе [reaction kind=ricochet]</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1092,7 +1080,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1102,63 +1090,63 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>o28</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Клещи</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>o63</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Голый запас</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Имей свои войска на двух гексах, соседних с одним и тем же гексом, где есть войска противника</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Замкни эти клещи с трёх сторон</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Имей в запасе ноль войск одного рода — весь род стоит на поле</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Так стоят сразу два рода</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>4 трофей</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Имей свои войска на двух гексах, соседних с одним и тем же гексом, где есть войска противника, — награда 6 боеприпасов и 1 трофей. Замкни клещи с трёх сторон, и условие усилено: 4 трофея. Клещи не бьют — они отнимают выход.</t>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце [reaction kind=return_fire]</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Имей в запасе ноль войск одного рода — весь род стоит на поле, — награда 1 трофей и 2 карты задания. Если так стоят сразу два рода, условие усилено: 4 трофея. Вывести род целиком значит подставить его целиком: в запасе не осталось никого, кем заменить убитого.</t>
         </is>
       </c>
     </row>
@@ -1168,119 +1156,119 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>o29</t>
+          <t>o33</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Пустой двор</t>
+          <t>Биржа</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Имей три своих войска вне гексов, где стоят твои здания, и ни одного своего войска на этих гексах</t>
+          <t>В ЭТОТ ХОД оплати три разных предложения на планшете рынка — напечатанные курсы и предложения карт сделок считаются по отдельности</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Все три стоят на разных гексах</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>6 монет, 1 трофей</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>assembly модуль</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
+          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain ammo=1 order=operation]</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Имей три своих войска вне гексов, где стоят твои здания, и ни одного своего войска на этих гексах, — награда 8 монет и 1 трофей. Если все три стоят на разных гексах, условие усилено: жетон модуля сборки. Двор пустеет ровно тогда, когда фронт наконец поехал.</t>
+          <t>В ЭТОТ ХОД оплати три разных предложения на планшете рынка — напечатанные курсы и предложения карт сделок считаются по отдельности. Награда: 6 монет и 1 трофей. Усиления у карты нет: печатных обменов на планшете осталось два, и три предложения набираются впритык — два печатных плюс одно с карты.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>o41</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Ответный удар</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>incident</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь жетон противника войском, которое в этот ход не перемещалось</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Это войско стоит на гексе, где есть твоё здание</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6 трофей</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь жетон противника войском, которое в этот ход не перемещалось, — награда 6 боеприпасов и 1 трофей. Если это войско стоит на гексе, где есть твоё здание, условие усилено: 6 трофеев. Ответный удар — это удар с места: враг подошёл сам, а ты не сходил с позиции и не разменял её на манёвр.</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>o36</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Научный рывок</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Дойди до второго шага хотя бы на одном треке технологий</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Стой на втором шаге сразу на двух треках</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>6 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>1 карта арсенала</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Дойди до второго шага хотя бы на одном треке технологий — награда 6 монет и 1 трофей. Стой на втором шаге сразу на двух треках, и условие усилено: 1 карта арсенала. Второй шаг — первое место, где трек начинает платить очками.</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1278,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>o42</t>
+          <t>o34</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Разорение</t>
+          <t>Научный отдел</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1305,104 +1293,104 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь добытчик противника</t>
+          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД этот добытчик был запитан</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>4 монет, 1 трофей</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>attack модуль</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
+          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain ammo=1 order=operation]</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
+          <t>В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь добытчик противника — награда 6 монет и 1 трофей. Если этот добытчик был запитан, условие усилено: жетон модуля атаки. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи.</t>
+          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением. Награда: 4 монеты и 1 трофей. Усиления у карты нет: на планшете науки три обмена, и три предложения — это ровно все они за один ход.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>o43</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Охота на сильного</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>o64</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Разнос трофеев</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтоженный жетон был зданием</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>6 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>4 трофей</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда 6 боеприпасов и 1 трофей. Если уничтоженный жетон был зданием, условие усилено: 4 трофея. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД сдай трофеи на ДВУХ разных треках технологий</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>На трёх треках</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 4 карт задания</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 1 трофей и 4 карты задания. На трёх треках условие усилено. Одно действие Науки двигает один трек, поэтому два трека — это два захода в науку за ход.</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1400,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>o46</t>
+          <t>o17</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Трофейный обоз</t>
+          <t>Штаб на передовой</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1427,12 +1415,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетоны трёх разных видов</t>
+          <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Собери четыре разных вида</t>
+          <t>Твоих зданий вокруг чужого ЦУ два, и стоят они на разных гексах</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1442,7 +1430,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>assembly модуль</t>
+          <t>4 трофей</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1453,200 +1441,200 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетоны трёх разных видов — пехота, техника, авиация, вышка и каждый тип здания считаются отдельно. Награда: 6 монет и 1 трофей. Собери четыре разных вида, и условие усилено: жетон модуля сборки. Обоз показывает не силу удара, а широту фронта.</t>
+          <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника, — награда 6 монет и 1 трофей. Если таких твоих зданий два и стоят они на разных гексах, условие усилено: 4 трофея. Подобраться стройкой к чужому штабу дороже, чем кажется: туда ещё надо дойти, и там по тебе будут бить.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>o01</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Полный залп</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>o11</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Передовая база</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД действием Снаряжение произведи боеприпасы не меньше чем двумя своими зданиями и не произведи ни одного войска</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Среди этих зданий есть завод или авиабаза</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД построй его на гексе, соседнем с гексом, где есть здание противника</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>6 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>1 карта арсенала</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ ДОБЫЧА [free_action action=mining]</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД действием Снаряжение произведи боеприпасы не меньше чем двумя своими зданиями и не произведи ни одного войска. Награда: 4 монеты и 1 трофей. Если среди этих зданий есть завод или авиабаза, условие усилено: 1 карта арсенала. Ход без единого нового войска — цена полного залпа.</t>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда 6 монет и 1 трофей. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 карта арсенала. Передовая база строится под огнём — потому и платит.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>o02</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Конвейер</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>o18</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Полная нагрузка</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Доведи число зданий до четырёх, сохранив запитанность всех</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1 карта арсенала</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ [reaction kind=battle_first]</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх, — награда 6 монет и 1 трофей. Доведи число зданий до четырёх, сохранив запитанность всех, и условие усилено: 1 карта арсенала. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>o65</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Перестройка</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД найми два войска разных родов</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Среди нанятых есть авиация и нет ни одной вышки</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>4 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>6 трофей</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД снеси своё здание и построй другое</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Построенное встало на тот же гекс, где стояло снесённое</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2 трофей</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД найми два войска разных родов — награда 4 боеприпаса и 1 трофей. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 6 трофеев. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>o04</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Жила</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Оба примыкают к нестартовым тайлам зарождения</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>attack модуль</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения, — награда 10 монет и 1 трофей. Если оба примыкают к нестартовым тайлам зарождения, условие усилено: жетон модуля атаки. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД снеси своё здание и построй другое — награда 1 трофей и 2 карты задания. Если построенное встало на тот же гекс, где стояло снесённое, условие усилено: 2 трофея. Здание не переезжает: его сносят и ставят заново, и обе операции стоят действия.</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1644,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>o05</t>
+          <t>o15</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Выработка</t>
+          <t>Стройбум</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1671,22 +1659,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения</t>
+          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Этим ты полностью исчерпал зарождение, и тайл ушёл с поля</t>
+          <t>Выполни три операции на трёх попарно несоседних гексах</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>6 БПР, 1 трофей</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>assembly модуль</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1697,78 +1685,78 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ: ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения — награда 6 монет и 1 трофей. Если ты этим полностью исчерпал зарождение и тайл ушёл с поля, условие усилено: жетон модуля сборки. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
+          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой, — награда 6 боеприпасов и 1 трофей. Выполни три операции на трёх попарно несоседних гексах, и условие усилено: 2 трофея. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>o08</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Разведка недр</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>o12</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Наглая стройка</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД забери печатный контейнер добытчиком</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>За весь ход ты не добыл ни одного келемия</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>4 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1 карта арсенала</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ ДОБЫЧА [free_action action=mining]</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД забери печатный контейнер добытчиком — награда 4 монеты и 1 трофей. Если при этом за весь ход ты не добыл ни одного келемия, условие усилено: 1 карта арсенала. Каждый добытчик в Добыче выбирает одно: келемий или контейнер.</t>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД на этом гексе два и более жетонов противника</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>8 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>4 трофей</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника, — награда 8 монет и 1 трофей. Если на этом гексе два и более жетонов противника, условие усилено: 4 трофея. Стройка под чужим стволом — заявка, а не расчёт.</t>
         </is>
       </c>
     </row>
@@ -1778,119 +1766,123 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>o15</t>
+          <t>o20</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Стройбум</t>
+          <t>Коммутация</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>incident</t>
+          <t>state</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой</t>
+          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Выполни три операции на трёх попарно несоседних гексах</t>
+          <t>Держи так три источника</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>8 монет, 1 трофей</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>assembly модуль</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ [reaction kind=battle_first]</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой, — награда 6 боеприпасов и 1 трофей. Выполни три операции на трёх попарно несоседних гексах, и условие усилено: 4 трофея. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
+          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух, — награда 8 монет и 1 трофей. Держи так три источника, и условие усилено: жетон модуля сборки. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному на каждом неудобно намеренно.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>o16</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Переезд</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>incident</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй здание на гексе, где у тебя не было ни одного своего здания</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД снеси при этом своё здание на другом гексе</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1 карта арсенала</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй здание на гексе, где у тебя не было ни одного своего здания, — награда 6 монет и 1 трофей. Если в этот же ход ты снёс своё здание на другом гексе, условие усилено: 1 карта арсенала. Переезда как операции в Стройке нет: хозяйство переезжает стройкой на новом месте и сносом на старом, и обе половины платные.</t>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>o66</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Списание</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>sacrifice</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Сбрось карту арсенала</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>4 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>attack модуль</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>платит: 1 arsenal_cards</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце [reaction kind=return_fire]</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Сбрось карту арсенала — награда 4 монеты и 1 трофей. Сбрось вторую, и условие усилено: жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
         </is>
       </c>
     </row>
@@ -1900,32 +1892,32 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>o18</t>
+          <t>o67</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Полная нагрузка</t>
+          <t>Разрядка</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>sacrifice</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх</t>
+          <t>Сдай в общий запас 2 боеприпаса</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Доведи число зданий до четырёх, сохранив запитанность всех</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>1 трофей, 2 карт задания</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1933,86 +1925,94 @@
           <t>1 карта арсенала</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>платит: 2 ammo</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
+          <t>ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс [reaction kind=withdraw]</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>В МОМЕНТЕ: ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх, — награда 8 монет и 1 трофей. Доведи число зданий до четырёх, сохранив запитанность всех, и условие усилено: 1 карта арсенала. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
+          <t>Сдай в общий запас 2 боеприпаса — награда 1 трофей и 2 карты задания. Сдай пять, и условие усилено: карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>o19</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Военпром</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Имей два своих военных здания на разных гексах, примыкающих друг к другу общей стенкой</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Вытяни цепочку из трёх своих зданий, примыкающих друг к другу</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1 карта арсенала</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Имей два своих военных здания на разных гексах, примыкающих друг к другу общей стенкой, — награда 6 монет и 1 трофей. Вытяни такую цепочку из трёх своих зданий, и условие усилено: 1 карта арсенала. Здание, повёрнутое стенкой к соседнему гексу, и растит зону стройки, и держит эту цепочку.</t>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>o10</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Разоружение</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>sacrifice</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Верни в свой запас два своих войска с поля</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Это техника и/или авиация, и оба жетона с одного гекса</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>6 БПР, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>assembly модуль</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>платит: 2 units_on_field</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Верни в свой запас два своих войска с поля — награда 6 боеприпасов и 1 трофей. Если это техника и/или авиация и оба жетона с одного гекса, условие усилено: жетон модуля сборки. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
         </is>
       </c>
     </row>
@@ -2022,119 +2022,123 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>o20</t>
+          <t>o06</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Коммутация</t>
+          <t>Отгрузка</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>sacrifice</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух</t>
+          <t>Сдай два своих неоткрытых контейнера</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Держи так три источника</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>6 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4 трофей</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>платит: 2 container</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain ammo=1 order=operation]</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Сдай два своих неоткрытых контейнера — награда 6 монет и 1 трофей. Сдай четыре, и условие усилено: 4 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>o68</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Бронебой</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>incident</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь технику или авиацию противника</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>И ещё два любых чужих жетона</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
           <t>8 монет, 1 трофей</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>assembly модуль</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух, — награда 8 монет и 1 трофей. Держи так три источника, и условие усилено: жетон модуля сборки. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному на каждом неудобно намеренно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>o34</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Научный отдел</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>incident</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Возьми четыре разных предложения</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>1 карта арсенала</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ РЫНОК [free_action action=market]</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением. Награда: 2 монеты и 1 трофей. Возьми четыре разных предложения, и условие усилено: 1 карта арсенала. Больше одного шага на трек за действие не сделать — значит придётся идти вширь.</t>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) [exchange_science_or_market amount=1]</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь технику или авиацию противника — награда 8 монет и 1 трофей. Если снял ещё два любых чужих жетона, условие усилено: карта арсенала. Техника и авиация дороже прочего и стоят дальше от чужих стен: до них ещё надо дотянуться.</t>
         </is>
       </c>
     </row>
@@ -2144,27 +2148,27 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>o36</t>
+          <t>o69</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Научный рывок</t>
+          <t>Зачистка гекса</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Дойди до второго шага хотя бы на одном треке технологий</t>
+          <t>В ЭТОТ ХОД уничтожь все жетоны противника на одном гексе</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Стой на втором шаге сразу на двух треках</t>
+          <t>Их на этом гексе было не меньше трёх</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2174,89 +2178,89 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1 карта арсенала</t>
+          <t>attack модуль</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) [exchange_science_or_market amount=1]</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Дойди до второго шага хотя бы на одном треке технологий — награда 8 монет и 1 трофей. Стой на втором шаге сразу на двух треках, и условие усилено: 1 карта арсенала. Второй шаг — первое место, где трек начинает платить очками.</t>
+          <t>В ЭТОТ ХОД уничтожь все жетоны противника на одном гексе — награда 8 монет и 1 трофей. Если их там было не меньше трёх, условие усилено: жетон модуля атаки. Вычистить гекс целиком — работа не одного выстрела: здание закрывает гекс, и снимать приходится по очереди.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>o40</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Ва-банк</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Имей одновременно ноль монет и ноль боеприпасов</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Обнули заодно и келемий</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>6 трофей</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Имей одновременно ноль монет и ноль боеприпасов — награда 6 монет и 1 трофей. Обнули заодно и келемий, и условие усилено: 6 трофеев. Ва-банк играют только на голом столе.</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>o42</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Разорение</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>incident</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь добытчик противника</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД этот добытчик был полностью запитан и примыкал к келемию</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>8 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>attack модуль</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) [exchange_science_or_market amount=1]</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь добытчик противника — награда 8 монет и 1 трофей. Если этот добытчик был полностью запитан и примыкал к келемию, условие усилено: жетон модуля атаки. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи — а работающий на полную вдвое дороже.</t>
         </is>
       </c>
     </row>
@@ -2266,27 +2270,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>o06</t>
+          <t>o25</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Отгрузка</t>
+          <t>Осада</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>sacrifice</t>
+          <t>state</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Сдай два своих неоткрытых контейнера</t>
+          <t>Имей среди уничтоженных жетонов жетон противника</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Их два, и один из них — добытчик</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2299,94 +2303,86 @@
           <t>attack модуль</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>платит: 2 container</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНЫЙ РЫНОК [free_action action=market]</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас [reaction kind=evacuate_trophy]</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Сдай два своих неоткрытых контейнера — награда 8 монет и 1 трофей. Сдай третий, и условие усилено: жетон модуля атаки. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
+          <t>Имей среди уничтоженных жетонов жетон противника — награда 8 монет и 1 трофей. Если их два и один из них добытчик, условие усилено: жетон модуля атаки. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>o10</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Разоружение</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>sacrifice</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Верни в свой запас два своих войска с разных гексов, не считая вышек и не считая гексов со своими зданиями</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>6 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4 трофей</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>платит: 2 units_off_base</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Верни в свой запас два своих войска с разных гексов, не считая вышек и не считая гексов со своими зданиями, — награда 6 монет и 1 трофей. Верни третье с третьего гекса, и условие усилено: 4 трофея. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>o70</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Обесточивание</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Имей среди уничтоженных жетонов два жетона противника</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Один из них — энергостанция</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>8 монет, 1 трофей</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>assembly модуль</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце [reaction kind=barrage]</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Имей среди уничтоженных жетонов два жетона противника — награда 8 монет и 1 трофей. Если один из них энергостанция, условие усилено: жетон модуля сборки. Энергостанция питает всё остальное, поэтому её снос стоит противнику дороже собственной цены.</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2392,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>o50</t>
+          <t>o71</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Линия фронта</t>
+          <t>Две войны</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2411,104 +2407,104 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Твои войска образуют непрерывное соседство, связывающее два разных гекса, где стоят твои добытчики</t>
+          <t>Имей среди уничтоженных жетонов жетоны ДВУХ разных противников</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>В этом соседстве не участвует ни одна вышка</t>
+          <t>И оба этих жетона — здания</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>8 монет, 1 трофей</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6 трофей</t>
+          <t>assembly модуль</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) [exchange_science_or_market amount=1]</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Твои войска образуют непрерывное соседство, связывающее два разных гекса, где стоят твои добытчики, — награда 6 боеприпасов и 1 трофей. Если в этом соседстве не участвует ни одна вышка, условие усилено: 6 трофеев. Вышка стоит даром и не двигается — линия без вышек означает, что ты держишь её живыми войсками.</t>
+          <t>Имей среди уничтоженных жетонов жетоны двух разных противников — награда 8 монет и 1 трофей. Если оба этих жетона здания, условие усилено: жетон модуля сборки. Единственная карта колоды, которую нельзя закрыть, воюя с одним соседом.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>o53</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Промышленный узел</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Твои здания образуют непрерывное соседство, связывающее три гекса, лежащих по прямой</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>В этом соседстве участвуют две твои авиабазы</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>6 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>6 трофей</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Твои здания образуют непрерывное соседство, связывающее три гекса, лежащих по прямой, — награда 6 монет и 1 трофей. Если в этом соседстве участвуют две твои авиабазы, условие усилено: 6 трофеев. Авиабаза просит три кубика энергии, и две подряд — это уже вся сеть.</t>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>o72</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Против сильнейшего</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>incident</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Уничтоженный жетон был техникой или авиацией</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2 трофей</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>РЕМОНТ ГЕКСА [heal_hex]</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя, — награда 1 трофей и 2 карты задания. Если уничтоженный был техникой или авиацией, условие усилено: 2 трофея. Бить сильнейшего значит получить сдачи, и карта платит именно за это.</t>
         </is>
       </c>
     </row>
@@ -2518,32 +2514,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>o55</t>
+          <t>o21</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Периметр</t>
+          <t>Первая кровь</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее два гекса у края поля — гекса, у которого хотя бы одно ребро не имеет соседнего гекса</t>
+          <t>В ЭТОТ ХОД уничтожь два жетона противника</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>В этом соседстве участвует твоя авиабаза</t>
+          <t>В ЭТОТ ХОД у одного из уничтоженных прочность была 2 или больше</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10 монет, 1 трофей</t>
+          <t>8 монет, 1 трофей</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2554,83 +2550,83 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) [exchange_science_or_market amount=1]</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее два гекса у края поля — гекса, у которого хотя бы одно ребро не имеет соседнего гекса. Награда: 10 монет и 1 трофей. Если в этом соседстве участвует твоя авиабаза, условие усилено: жетон модуля атаки.</t>
+          <t>В ЭТОТ ХОД уничтожь два жетона противника — награда 8 монет и 1 трофей. Если у одного из них прочность была 2 или больше, условие усилено: жетон модуля атаки. Первая кровь считается по двум, а не по одному.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>o56</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Прорыв</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее одно из твоих зданий со зданием противника, и его длина не меньше 4 гексов</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Длина этого соседства не меньше 6 гексов</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>8 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>4 трофей</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее одно из твоих зданий со зданием противника, и его длина не меньше 4 гексов, — награда 8 боеприпасов и 1 трофей. Если длина не меньше 6 гексов, условие усилено: 4 трофея. Дорога до чужого двора — это и путь снабжения, и готовая линия удара.</t>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>o43</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Охота на сильного</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>incident</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтоженный жетон был зданием</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>2 трофей</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас [reaction kind=evacuate_trophy]</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда 1 трофей и 2 карты задания. Если уничтоженный жетон был зданием, условие усилено: 2 трофея. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
         </is>
       </c>
     </row>
@@ -2640,32 +2636,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>o57</t>
+          <t>o73</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Дорога между дворами</t>
+          <t>Диверсия</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее гексы, примыкающие к тайлам стартового зарождения</t>
+          <t>В ЭТОТ ХОД уничтожь энергостанцию противника</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>В этом соседстве участвует не меньше 3 жетонов войск</t>
+          <t>Это была энергостанция третьего или четвёртого уровня</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1 трофей, 2 келемий</t>
+          <t>1 трофей, 2 карт задания</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2676,83 +2672,83 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>СВОБОДНАЯ ДОБЫЧА [free_action action=mining]</t>
+          <t>РЕМОНТ ГЕКСА [heal_hex]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>СПЕЦ ДЕЙСТВИЕ: СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее гексы, примыкающие к тайлам стартового зарождения, — награда 1 трофей и 2 келемия. Если в соседстве участвует не меньше 3 жетонов войск, условие усилено: 4 трофея. Стартовые зарождения стоят у баз, так что эта дорога всегда идёт по чужим задворкам.</t>
+          <t>В ЭТОТ ХОД уничтожь энергостанцию противника — награда 1 трофей и 2 карты задания. Если это была энергостанция третьего или четвёртого уровня, условие усилено: 4 трофея. Крупные энергостанции стоят в глубине, и лезть за ними опасно.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>o58</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Живая цепь</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>o74</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Энергосеть</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Твои ВОЙСКА образуют непрерывное соседство, связывающее две ячейки у границ поля</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>В этом соседстве не участвует ни одна вышка</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>6 БПР, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>assembly модуль</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Твои войска образуют непрерывное соседство, связывающее две ячейки у границ поля, — награда 6 боеприпасов и 1 трофей. Если в соседстве не участвует ни одна вышка, условие усилено: жетон модуля сборки. Вышка стоит даром и не двигается — линия без вышек значит, что ты держишь её живыми войсками.</t>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Имей на поле все свои энергостанции</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 4 карт задания</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ [reaction kind=battle_first]</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Имей на поле все свои энергостанции — награда 1 трофей и 4 карты задания. Полный комплект источников на поле — лучшая мишень в партии: их нечем прикрыть и негде спрятать.</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2758,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>o59</t>
+          <t>o75</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Промышленная связка</t>
+          <t>Рудный двор</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2777,104 +2773,104 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Твои ЗДАНИЯ образуют непрерывное соседство, связывающее два гекса, где стоят твои добытчики</t>
+          <t>Имей на поле все свои добытчики</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>В этом соседстве участвует твоя энергостанция</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>1 трофей, 4 карт задания</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6 трофей</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ [reaction kind=battle_first]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Твои здания образуют непрерывное соседство, связывающее два гекса, где стоят твои добытчики, — награда 8 монет и 1 трофей. Если в соседстве участвует твоя энергостанция, условие усилено: 6 трофеев. Связка из зданий заодно растит зону стройки — она платит дважды.</t>
+          <t>Имей на поле все свои добытчики — награда 1 трофей и 4 карты задания. Разложил всё, чем добываешь, — держи оборону или жги карту: у добытчика прочность один.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>o60</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Клин</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее одно из твоих зданий со зданием противника, и в нём не участвует авиация</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>В этом соседстве участвуют и пехота, и техника</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2 монет, 1 трофей</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>1 карта арсенала</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее одно из твоих зданий со зданием противника, и в нём не участвует авиация, — награда 2 монеты и 1 трофей. Если в соседстве участвуют и пехота, и техника, условие усилено: 1 карта арсенала. Авиация перелетает разрывы; клин по земле приходится выкладывать целиком.</t>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>o02</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Конвейер</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>incident</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД найми два войска разных родов</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Среди нанятых есть авиация и нет ни одной вышки</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>4 трофей</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>В ЭТОТ ХОД найми два войска разных родов — награда 1 трофей и 2 карты задания. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 4 трофея. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2880,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>o61</t>
+          <t>o76</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Широкий фронт</t>
+          <t>Расселение</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2899,12 +2895,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее три ячейки у границ поля</t>
+          <t>Займи войсками четыре разных гекса, и родов среди них не меньше двух</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Длина этого соседства не меньше 6 гексов</t>
+          <t>Шесть гексов</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2914,89 +2910,89 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>attack модуль</t>
+          <t>4 трофей</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
+          <t>РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе [reaction kind=ricochet]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>строка таблицы не найдена</t>
+          <t>В МОМЕНТЕ: РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>РАСХОЖДЕНИЕ</t>
+          <t>сходится</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее три ячейки у границ поля, — награда 6 монет и 1 трофей. Если длина соседства не меньше 6 гексов, условие усилено: жетон модуля атаки. Три края разом держит только тот, у кого фронт шире чужого.</t>
+          <t>Займи войсками четыре разных гекса, и родов среди них не меньше двух, — награда 6 монет и 1 трофей. Шесть гексов, и условие усилено: 4 трофея. Растянуться по полю выгодно и опасно разом: где тонко, там и порвут.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>o62</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Обход</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>o77</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Растяжка</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее два противоположных гекса вокруг одного тайла зарождения</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Длина этого соседства не меньше 5 гексов</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1 трофей, 2 келемий</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>assembly модуль</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее два противоположных гекса вокруг одного тайла зарождения, — награда 1 трофей и 2 келемия. Если длина соседства не меньше 5 гексов, условие усилено: жетон модуля сборки. Обход вокруг жилы отрезает соседа от келемия, не потратив ни одного боеприпаса.</t>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Займи войсками пять разных гексов</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>На двух из них есть здания противника</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>1 трофей, 2 карт задания</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>1 карта арсенала</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ [reaction kind=battle_first]</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Займи войсками пять разных гексов — награда 1 трофей и 2 карты задания. Если на двух из них есть здания противника, условие усилено: 1 карта арсенала. Гекс с чужим зданием закрыт: стоять там можно, бить оттуда — только по зданиям и вышкам.</t>
         </is>
       </c>
     </row>
@@ -3079,600 +3075,600 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>n1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Подъём</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Имей на поле не меньше трёх своих зданий, считая ЦУ</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>+1 монета [gain coin=1]</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Имей на поле не меньше трёх своих зданий, считая ЦУ, — награда трофей и карта задания. Считается и ЦУ, поэтому от подготовки до выполнения ровно две стройки.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>n2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Первый боец</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД найми войско любого рода, кроме вышки</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>+1 боеприпас [gain ammo=1]</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД найми войско любого рода, кроме вышки, — награда трофей и карта задания. Вышка не считается: её ЦУ собирает даром, и наймом это назвать нельзя.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>n3</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Патроны</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Имей не меньше трёх боеприпасов</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>+1 монета [gain coin=1]</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Имей не меньше трёх боеприпасов — награда трофей и карта задания. Порог три, а не два: один боеприпас у тебя уже есть с подготовки.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>n4</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Первая сделка</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД воспользуйся предложением карты сделок на рынке</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>+1 боеприпас [gain ammo=1]</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД воспользуйся предложением карты сделок на рынке — награда трофей и карта задания. Напечатанный курс не подходит: карта требует именно предложения карты сделок.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>n5</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Коммутация</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Имей на поле запитанное здание, стоящее не на гексе с твоим ЦУ</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>+1 монета [gain coin=1]</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Имей на поле запитанное здание, стоящее не на гексе с твоим ЦУ, — награда трофей и карта задания. Энергия до соседнего гекса сама не дотянется: её надо туда перекинуть Сменой энергии.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>n6</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Имей на поле своё войско на расстоянии двух и больше гексов от гекса с твоим ЦУ</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>+1 боеприпас [gain ammo=1]</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Имей на поле своё войско на расстоянии двух и больше гексов от гекса с твоим ЦУ — награда трофей и карта задания. Вышка неподвижна, так что выйти придётся кем-то живым.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>n7</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Жила</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Имей не меньше трёх келемия</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>+1 монета [gain coin=1]</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Имей не меньше трёх келемия — награда трофей и карта задания. Келемий равен победному очку, поэтому держать его дорого, а тратить жалко.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>n8</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Находка</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Имей у себя не меньше двух неоткрытых контейнеров</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>+1 боеприпас [gain ammo=1]</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Имей у себя не меньше двух неоткрытых контейнеров — награда трофей и карта задания. Вскрытый контейнер сразу уходит, так что придётся терпеть и не открывать.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>n9</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Первый шаг</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Стой хотя бы на первом шаге любого трека технологий</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>+1 монета [gain coin=1]</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Стой хотя бы на первом шаге любого трека технологий — награда трофей и карта задания. За действие Наука больше одного шага на трек не сделать, поэтому начинают все с одного и того же.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>n10</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Первый трофей</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Имей среди уничтоженных жетонов хотя бы один жетон</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>+1 боеприпас [gain ammo=1]</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Имей среди уничтоженных жетонов хотя бы один жетон — награда трофей и карта задания. Трофей берут только с боя, поэтому карта платит за первый настоящий выстрел.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>n11</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Второй заход</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД получи действие с нижнего приказа своей карты приказа</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>+1 монета [gain coin=1]</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД получи действие с нижнего приказа своей карты приказа — награда трофей и карта задания. Нижний приказ открывается не всегда, так что карту держат до подходящего раунда.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>n12</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>В унисон</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>incident</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД сыграй верхом тот же приказ, что и другой игрок</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1 трофей, 1 карт задания</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>+1 боеприпас [gain ammo=1]</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД сыграй верхом тот же приказ, что и другой игрок, — награда трофей и карта задания. Совпавший приказ не срабатывает, так что эта карта — плата за потерянное действие.</t>
         </is>
@@ -3739,595 +3735,595 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>s5_01</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Смотр войск</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2 ПО за каждый РАЗНЫЙ род войск у тебя на поле. Потолок 8.</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Держи три РАЗНЫХ рода войск одновременно на ОДНОМ гексе.</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Найми бесплатно по одному жетону КАЖДОГО рода войск на свои гексы, без энергии и зданий.</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Парад — это заявление: смотри, у меня есть всё. Множитель платит за разнообразие войск в финале, поэтому одного танкового кулака мало. Требование сгоняет три разных рода на один гекс, а награда разом достраивает армию до полного набора, минуя энергию и здания.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>s5_02</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Дальний рубеж</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>1 ПО за каждое своё войско на гексе, соседнем с чужим зданием. Потолок 5.</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Поставь своё войско на гекс, соседний с ЧУЖИМ ЦУ.</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Перенеси любые свои войска на один гекс поля и сними с них весь урон.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Стоять у чужого порога дорого и выгодно одновременно. Множитель считает войска у чужих зданий, требование зовёт к самому чужому ЦУ, а награда собирает уцелевших в один кулак и лечит их — чтобы после дерзости было чем воевать.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>s5_03</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Раскинутая сеть</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>1 ПО за каждый РАЗНЫЙ гекс, где стоит твоё здание. Потолок 6.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Имей свои здания на пяти РАЗНЫХ гексах.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Построй три здания бесплатно, игнорируя энергию и зону стройки.</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Не крепость, а сеть: множитель платит за КОЛИЧЕСТВО занятых гексов, а не за уровень зданий. Требование просит пять разных гексов, награда достраивает сеть тремя бесплатными зданиями без энергии и без зоны стройки.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>s5_04</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Гарнизонная служба</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2 ПО за каждый гекс, где стоят одновременно твоё здание и твоё войско. Потолок 6.</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Имей три гекса, где стоят одновременно твоё здание и твоё войско.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Сыграй подряд ДВА полных приказа со своей руки, оба целиком.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Гарнизон — это здание с охраной. Множитель платит за гексы, где стоят и здание, и войско; требование просит три таких гекса. Награда даёт то, чего в игре не купить, — два полных приказа подряд.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>s5_05</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Архив штаба</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2 ПО за каждое выполненное задание сверх трёх. Потолок 6.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Выполни четыре задания за партию.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Возьми ВСЕ карты с витрины арсенала в руку и добери две карты задания.</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Штабной архив живёт закрытыми делами. Множитель платит за задания сверх трёх, то есть у карты есть порог, ниже которого она молчит. Награда забирает витрину арсенала целиком и добавляет два новых задания.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>s5_06</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Оружейная палата</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>2 ПО за каждую установленную карту арсенала сверх двух. Потолок 6.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Держи три установленные карты арсенала одновременно.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Сожги любое число установленных у себя карт арсенала и получи все их утиль-эффекты разом.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Палата ценит не выстрел, а арсенал на стене. Множитель платит за установленные карты сверх двух, требование просит держать три разом. Награда переворачивает смысл: сожги их все и получи все утиль-эффекты в один ход.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>s5_07</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Золотая жила</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>1 ПО за каждый келемий в твоём хранилище в конце партии. Потолок 5.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Имей пять келемия в хранилище одновременно.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Обменяй весь свой келемий по курсу «за каждый — любое действие бесплатно, вне очереди».</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Жила платит за то, что обычно тратят: множитель считает келемий, ОСТАВШИЙСЯ в хранилище к финалу. Требование просит собрать пять разом, а награда обменивает запас на бесплатные действия вне очереди — то есть даёт истратить его с двойной пользой.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>s5_08</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Первая линия</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>2 ПО за каждый трек науки, где твоя фишка выше всех. Потолок 6.</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Стой выше всех соперников сразу на ДВУХ треках науки.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Сделай четыре шага науки бесплатно, в любом порядке и по любым трекам.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Первая линия — про первенство, а не про высоту: множитель платит за треки, где ты выше ВСЕХ. Требование просит быть первым на двух треках сразу, награда добавляет четыре бесплатных шага науки в любом порядке.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>s5_09</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Трофейный обоз</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1 ПО за каждый уничтоженный тобой чужой жетон, пока твоё ЦУ ни разу не разрушено. Потолок 6.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Уничтожь четыре чужих жетона, ни разу не потеряв своё ЦУ.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Уничтожь любое чужое здание на поле без боя (кроме ЦУ) и забери его на место уничтоженных жетонов.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Обоз считает чужие потери, но только пока цело своё ЦУ: один разрушенный штаб — и множитель гаснет весь. Требование просит четыре чужих жетона, награда снимает с поля чужое здание вообще без боя.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>s5_10</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Штабная игра</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>2 ПО за каждый раунд, в котором ты был первым игроком. Потолок 6.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Будь первым игроком в двух раундах партии.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Забери жетон первого игрока и немедленно сыграй один полный приказ, пока остальные ждут.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Штабная игра платит за инициативу: множитель считает раунды, в которых ты был первым игроком. Требование просит два таких раунда, а награда забирает жетон первого игрока и тут же разыгрывает полный приказ, пока остальные ждут.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>s5_11</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Неприкосновенный запас</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2 ПО за каждое своё здание ПЕРВОГО уровня на поле в конце партии. Потолок 6.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Имей четыре своих здания первого уровня на поле одновременно.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Мгновенно подними два своих добытчика или энергостанции до четвёртого уровня.</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Запас — это то, что не пущено в дело: множитель платит за здания ПЕРВОГО уровня, стоящие на поле в финале. Требование просит четыре таких здания, а награда, наоборот, поднимает два из них сразу до четвёртого уровня — карта заставляет выбрать, что тебе дороже.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>s5_12</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Тень штаба</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>3 ПО, если твоё ЦУ ни разу не разрушено, плюс 1 ПО за каждого соперника, чьё ЦУ разрушали. Потолок 6.</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Твоё ЦУ цело, а ЦУ хотя бы одного соперника уже разрушено.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Уничтожь СВОЙ жетон уничтожения ЦУ — он уходит из игры навсегда, и снос твоего ЦУ не даёт сопернику ничего.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Тень штаба живёт чужой бедой: три очка за своё целое ЦУ и по одному за каждого соперника, чьё ЦУ разрушали. Требование выполняется само, как только чужой штаб пал первым. Награда убирает из игры твой жетон уничтожения ЦУ — снос твоего штаба перестаёт что-либо давать сопернику.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>s5_13</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Казна</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>1 ПО за каждые 2 монеты в твоём запасе в конце партии. Потолок 6.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Имей три гекса, где стоят одновременно твоё здание и твоё войско.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Сыграй подряд ДВА полных приказа со своей руки, оба целиком.</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>В базовых правилах монеты давали очко за пятёрку и давали всем. Теперь они не дают ничего никому — кроме того, кто взял эту карту, и ему платят вдвое лучше прежнего. Требование про здания с войсками нарочно не про деньги: копить и держать позицию приходится порознь.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>s5_14</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Склад лома</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>1 ПО за каждый несданный трофей у тебя в конце партии. Потолок 6.</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Поставь своё войско на гекс, соседний с ЧУЖИМ ЦУ.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Перенеси любые свои войска на один гекс поля и сними с них весь урон.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Трофеи сдают в Науку — и правильно делают, потому что несданные больше не стоят ничего. Эта карта переворачивает привычку: держать лом при себе становится выгоднее, чем менять его на шаги. Низ зовёт к чужому штабу, то есть туда, где лом и добывается.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>s5_15</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Промышленный узел</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>1 ПО за каждое своё здание на поле сверх двух. Потолок 6.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Держи три РАЗНЫХ рода войск одновременно на ОДНОМ гексе.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Найми бесплатно по одному жетону КАЖДОГО рода войск на свои гексы, без энергии и зданий.</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Раньше четыре здания давали очко всем. Теперь застройка не стоит ничего — кроме как у того, кто выбрал ею жить, и ему платят за каждое здание сверх двух. Требование про войска на одном гексе сознательно не про стройку: платят за застройку, а просят армию.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>s5_16</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Сводный полк</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>1 ПО за каждые 2 своих войска на поле в конце партии. Потолок 6.</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Имей пять келемия в хранилище одновременно.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Обменяй весь свой келемий по курсу «за каждый — любое действие бесплатно, вне очереди».</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Армия на поле снова стоит очков — но только у того, кто взял эту карту, и вдвое дороже прежнего. Держать войска живыми до финала теперь настоящая задача: ответного боя в правилах нет, и отбирать их будут охотно. Низ про келемий, чтобы карта не платила дважды за одно и то же.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>s5_17</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Тяжёлая промышленность</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>3 ПО за каждое своё здание ЧЕТВЁРТОГО уровня на поле в конце партии — добытчик и энергостанцию. Потолок 6.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Уничтожь четыре чужих жетона, ни разу не потеряв своё ЦУ.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Уничтожь любое чужое здание на поле без боя (кроме ЦУ) и забери его на место уничтоженных жетонов.</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Очки за здания четвёртого уровня были напечатаны на планшете и доставались всем, кто дотянул их до финала. Теперь это карта — и платит она втрое. Требование военное нарочно: тяжёлую промышленность оплачивает война, а награда сносит чужую фабрику без единого выстрела.</t>
         </is>
@@ -4401,30 +4397,30 @@
         <v>4</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>В МОМЕНТЕ</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4447,30 +4443,30 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>В МОМЕНТЕ</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4493,30 +4489,30 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>В МОМЕНТЕ</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4539,30 +4535,30 @@
         <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
+      <c r="E9" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -4585,30 +4581,30 @@
         <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
+      <c r="E11" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -4631,25 +4627,25 @@
         <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ВСЕГО В ДАННЫХ</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ ×6; СВОБОДНЫЙ БОЙ ×6; СВОБОДНЫЙ РЫНОК ×3; СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ ×5; СВОБОДНАЯ НАУКА ×5; СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ ×8; СВОБОДНАЯ ДОБЫЧА ×3; ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ ×4</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце ×3; ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс ×2; АТАКА ОДНИМ ВОЙСКОМ ×5; 1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта) ×6; ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце ×4; РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе ×2; +1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ ×3; СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ ×6; РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ ×5; ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас ×2; РЕМОНТ ГЕКСА ×2</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4732,1920 +4728,1920 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Выработка</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Оба примыкают к нестартовым тайлам зарождения</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>МОДУЛЬ АТАКИ</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Z · В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>низ выставляет два добытчика на виду, верх делает их снос платным: добытчик с прочностью 1 гибнет от первого удара — и ранит того, кто его снёс</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Выработка</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Этим ты полностью исчерпал зарождение, и тайл ушёл с поля</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>МОДУЛЬ СБОРКИ</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>D · В МОМЕНТЕ: ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>низ гонит добытчик к чужому зарождению, верх уводит жетон из-под удара: обе половины про выход из-под чужого хода, но сыграть можно одну</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Выработка</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Имей одновременно ноль монет и ноль боеприпасов</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Не имей даже келемий</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2 монет, 1 БПР</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1 ТРОФЕЙ</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>T · СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>задание требует пустых карманов, а атака — боеприпаса: верх прямо мешает низу, и это самый честный вид выбора</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Выработка</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>2 монет, 1 БПР</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>T · СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>три контейнера за ход — работа добытчиков; лишняя атака к ней ничего не добавляет, зато уводит от неё</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Выработка</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД произведи только боеприпасы и ни одного войска</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Эти здания - завод и авиабаза</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2 монет, 1 карт задания</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>X · СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>боеприпасов на планшете рынка больше нет вовсе (02.09.2026), так что обмен низ не закрывает даже отдалённо: он про келемий и трофеи, а низ про производство приказом</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Засада</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Имей два своих войска на гексах, где нет твоих зданий.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Четыре - и все стоят на разных гексах</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>2 монет, 1 карт задания</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>МОДУЛЬ СБОРКИ</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>O · В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>войска стоят без прикрытия и умрут первыми — зато не даром: каждое забирает с собой рану. Но сжёг верх — и держать двоих уже нечем</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Засада</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Имей на поле 2 свои вышки на разных гексах (обе не на гексе с ЦУ)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Одна из вышек стоит на гексе с жетонами врага</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>3 БПР</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>O · В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>вышка неподвижна и рано или поздно её снесут: пусть снос обойдётся сносящему в рану — но сжёг карту, и вторую вышку уже не додержать</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Засада</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Держи так сразу два своих войска</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>3 БПР</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Z · В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>вся карта про здание, за которым прячется войско: снесли укрытие — здание успевает выстрелить, а гарнизон выходит живым. Но сжёг верх, и держать позицию нечем</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Засада</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Имей своё войско на гексе, где есть здания врага</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Имей на одном таком гексе два своих войска</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>3 БПР</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>R · В МОМЕНТЕ: РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>войско стоит у врага под окнами, в чужой застройке и среди чужих жетонов — больше не заходят, а на гекс с чужими зданиями — заходят. И стоит там дорого: гекс закрыт чужим зданием, значит бить в нём можно только по зданиям и вышкам</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Засада</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Имей в запасе 0 войск одного вида</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Двух видов</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>O · В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>вывел весь род на поле — значит подставил его целиком; зато каждый убитый жетон достаётся врагу с раной в придачу</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Обеспечение</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>В этот ход воспользуйся тремя разными предложениями Рынка</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>A · В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>после снятия боеприпасов и ячейки энергии на планшете осталось ДВА печатных обмена, значит три предложения набираются ровно впритык: два печатных плюс одно с карты. Верх обязан быть скромным</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Обеспечение</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Дойди до второго шага хотя бы на одном треке технологий</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Стой на втором шаге сразу на двух треках</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>T · СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>наука и бой не пересекаются ничем: карта честно спрашивает, что тебе сейчас нужнее</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Обеспечение</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2 монет, 1 БПР</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>A · В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>на планшете науки три обмена (02.09.2026), значит три предложения — это ровно все они за один ход. Обмен в верх не дан нарочно: он закрывал бы низ сам</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Обеспечение</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД сдай трофеи на ДВУХ разных треках технологий</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>На трёх треках</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>2 карт задания</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>T · СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>два трека за ход — это два шага, оплаченных трофеями; атака сверху их не заменит — но пригодится тому, кому сдавать нечего</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Твоих зданий вокруг чужого ЦУ два, и стоят они на разных гексах</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>E · СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>подобраться зданием к чужому штабу — это стройка, а смена энергии её не заменит; зато выручит того, у кого стройка уже встала без питания</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД построй свое здание на гексе, соседнем с гексом, где есть войска врага</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>На том же соседнем гексе есть здание врага</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>E · СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>строишь у врага — питать придётся под огнём; смена энергии про это, но здание за тебя не поставит</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Все твои здания, требующие энергию, запитаны (не менее 3)</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Не менее 4 зданий</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>P · В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>разложил хрупкое хозяйство и боишься сноса — верх даёт ударить первым; но ударил, и карта ушла в костёр</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД снеси своё здание и построй другое</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Построенное встало на тот же гекс, где стояло снесённое</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>2 монет, 1 карт задания</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>1 ТРОФЕЙ</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>T · СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>перестройке атака не нужна; зато она нужна тому, кому перестраивать уже нечего</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД построй 2 здания на разных гексах</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>3  здания на разных и несоседних между собой гексах</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>3 БПР</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1 ТРОФЕЙ</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>E · СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>две стройки за ход и так съедают приказ; смена энергии их не заменяет, а достраивает картину</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>На этом гексе два и более жетонов врага</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>E · СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>строить под носом у врага — дело энергии и наглости, но не смены модулей: верх и низ не пересекаются</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Развертывание</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Имей на двух зданиях - источниках энергии ровно один свободный кубик</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>На трех источниках энергии</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>МОДУЛЬ СБОРКИ</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>P · В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>свободные кубики — это витрина для чужого удара; верх позволяет ударить раньше, чем ударят по ней</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Расплата</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Сбрось карту арсенала</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>2 карты арсенала</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>2 монет, 1 БПР</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>МОДУЛЬ АТАКИ</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>O · В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>низ платит картой арсенала, верх — тем, что карта уходит в костёр: обе половины про расставание с картой, и обе одновременно не сыграть</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Расплата</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Сдай в общий запас 2 боеприпаса</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>5 боеприпасов</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2 монет, 1 карт задания</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>D · В МОМЕНТЕ: ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>низ требует отдать боеприпасы, отход их не тратит вовсе — потому и уместен: остаться без патронов и всё-таки уйти из-под удара</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Расплата</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Верни в запас 2 своих войска с поля</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Технику и/или авиацию - и с одного гекса</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>3 БПР</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>МОДУЛЬ СБОРКИ</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>E · СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>войска уходят с поля — питать остаётся здания; смена энергии как раз об этом, а войска она не вернёт</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Расплата</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Сдай два своих неоткрытых контейнера</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>4 контейнера</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>A · В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>контейнеры сдаются закрытыми, и боеприпас им ничем не поможет: самый скромный верх достаётся заданию, которое платят чужой валютой</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь технику или авиацию врага</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>и еще 2 жетона любого врага</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>X · СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>обмен на планшете воевать не помогает — и потому не превращает карту в автомат; он выход для того, у кого бой не сложился</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>их на этом гексе не менее 3</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>МОДУЛЬ АТАКИ</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>X · СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>вычистить гекс целиком — работа боя; верх нарочно из другой области, иначе низ закрывался бы сам</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь добытчик противника</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Этот добытчик был полностью запитан и примыкал к келемию</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>МОДУЛЬ АТАКИ</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>X · СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>если чужой добытчик недосягаем, картой всё равно можно распорядиться — через обмен, а не через бой</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Имей среди уничтоженных жетонов жетон врага</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>два жетона, один из них - добытчик</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>МОДУЛЬ АТАКИ</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>V · В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>низ копит СВОИ трофеи, утиль отнимает ЧУЖОЙ: одна тема, разные стороны стола — и обе половины одновременно не сыграть</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Имей среди уничтоженных жетонов два жетона врага</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>один из них - энергостанция</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>МОДУЛЬ СБОРКИ</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Z · В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>низ копит чужие трофеи, верх защищает свои здания: одна война, но разные её концы</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Имей среди уничтоженных жетонов жетоны ДВУХ разных противников</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>И оба этих жетона — здания</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>МОДУЛЬ СБОРКИ</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>X · СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>ждать дорогой трофей долго — верх даёт не ждать, но тогда трофея не будет</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтоженный жетон был техникой или авиацией</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>2 монет, 1 карт задания</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>1 ТРОФЕЙ</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>H · СПЕЦ ДЕЙСТВИЕ: СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>бить сильнейшего по войскам — значит получить сдачи; верх лечит гекс целиком, но карту закрывает костёр</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь два жетона противника</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД у одного из уничтоженных прочность была 2 или больше</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>4 монет</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>МОДУЛЬ АТАКИ</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>X · СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>два жетона за ход требуют своего боя; обмен на планшете тут ничем не поможет и потому не отменяет выбор</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтоженный жетон был зданием</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>1 ТРОФЕЙ</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>V · В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>низ забирает чужой жетон себе в трофеи, верх не даёт забрать твой: одна и та же война с двух сторон стола, и обе половины сразу не сыграть</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Устранение</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД уничтожь энергостанцию противника</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Это была энергостанция 3 или 4 уровня.</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>H · СПЕЦ ДЕЙСТВИЕ: СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>лезть к чужой энергостанции опасно; снять весь урон на гексе — это спасение отряда вместо награды</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Экспансия</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Имей на поле все свои 4 здания энергостанций</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>2 карт задания</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>P · В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>четыре энергостанции на поле — лучшая мишень в партии; верх даёт ударить первым, но карту тогда не сдать</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Экспансия</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Имей на поле все свои 4 здания добытчиков</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2 карт задания</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>P · В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>то же положение с добытчиками: разложил всё — держи оборону или жги карту</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Экспансия</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>В ЭТОТ ХОД найми два войска разных родов</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Среди нанятых есть авиация и нет ни одной вышки</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>2 монет, 1 карт задания</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>E · СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>найм требует запитанных зданий — смена энергии рядом, но нанимать за тебя не станет</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Экспансия</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Займи 4 разных гекса войсками хотя бы 2 видов</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>6 гексов</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>3 монет</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2 ТРОФЕЯ</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>R · В МОМЕНТЕ: РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>низ раскидывает войска по чужим гексам, а рикошет тем и живёт, что на гексе тесно от чужих жетонов: положение одно, а пользы от него две</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Экспансия</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>СОСТОЯНИЕ</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Займи войсками 5 разных гексов</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>На 2 из них есть здания противника</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>АРСЕНАЛ</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>P · В МОМЕНТЕ: РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>растянулся по полю и стоишь в чужой застройке — верх даёт ударить первым, пока не ударили по тебе; но сжёг его, и пять гексов держать нечем</t>
         </is>
@@ -6662,7 +6658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6699,1059 +6695,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>o03</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Опорный пункт</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>o07</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Засада</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>o11</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Передовая база</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>o12</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Наглая стройка</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ РЫНОК [free_action action=market]</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>o17</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Штаб на передовой</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Имей своё военное здание на расстоянии не больше 2 гексов от гекса с ЦУ противника</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>o21</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Первая кровь</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь два жетона противника</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>o22</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Зачистка</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Имей среди уничтоженных жетонов здание противника и верни его владельцу</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>o25</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Осада</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Имей среди уничтоженных жетонов здание противника</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>o27</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>На чужом дворе</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Имей своё войско на гексе, где стоит здание противника</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>o28</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Клещи</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Имей свои войска на двух гексах, соседних с одним и тем же гексом, где есть войска противника</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>o29</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Пустой двор</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Имей три своих войска вне гексов, где стоят твои здания, и ни одного своего войска на этих гексах</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>o41</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Ответный удар</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь жетон противника войском, которое в этот ход не перемещалось</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>o42</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Разорение</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь добытчик противника</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>o43</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Охота на сильного</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>o46</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Трофейный обоз</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Имей среди уничтоженных жетонов жетоны трёх разных видов</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: 1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>o01</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Полный залп</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД действием Снаряжение произведи боеприпасы не меньше чем двумя своими зданиями и не произведи ни одного войска</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ ДОБЫЧА [free_action action=mining]</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>o04</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Жила</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>o05</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Выработка</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>o08</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Разведка недр</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД забери печатный контейнер добытчиком</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ ДОБЫЧА [free_action action=mining]</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>o15</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Стройбум</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>o16</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Переезд</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД построй здание на гексе, где у тебя не было ни одного своего здания</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>o18</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Полная нагрузка</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>o19</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Военпром</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Имей два своих военных здания на разных гексах, примыкающих друг к другу общей стенкой</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>o20</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Коммутация</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>o34</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Научный отдел</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ РЫНОК [free_action action=market]</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>o36</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Научный рывок</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Дойди до второго шага хотя бы на одном треке технологий</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>o40</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Ва-банк</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Имей одновременно ноль монет и ноль боеприпасов</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ: АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>o06</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Отгрузка</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Сдай два своих неоткрытых контейнера</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ РЫНОК [free_action action=market]</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>В МОМЕНТЕ: плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>o10</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Разоружение</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Верни в свой запас два своих войска с разных гексов, не считая вышек и не считая гексов со своими зданиями</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ [energy_or_modules]</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>o50</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Линия фронта</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Твои войска образуют непрерывное соседство, связывающее два разных гекса, где стоят твои добытчики</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>o53</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Промышленный узел</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Твои здания образуют непрерывное соседство, связывающее три гекса, лежащих по прямой</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>o55</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Периметр</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее два гекса у края поля — гекса, у которого хотя бы одно ребро не имеет соседнего гекса</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>o56</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Прорыв</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее одно из твоих зданий со зданием противника, и его длина не меньше 4 гексов</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНОЕ ДВИЖЕНИЕ [free_action action=movement]</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>o57</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Дорога между дворами</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее гексы, примыкающие к тайлам стартового зарождения</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ ДОБЫЧА [free_action action=mining]</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>o58</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Живая цепь</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Твои ВОЙСКА образуют непрерывное соседство, связывающее две ячейки у границ поля</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>o59</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Промышленная связка</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Твои ЗДАНИЯ образуют непрерывное соседство, связывающее два гекса, где стоят твои добытчики</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ [free_action buildings=1 action=assembly]</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>o60</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Клин</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее одно из твоих зданий со зданием противника, и в нём не участвует авиация</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНАЯ НАУКА [free_action action=science]</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>o61</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Широкий фронт</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее три ячейки у границ поля</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ [free_action ops=1 action=build]</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>o62</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Обход</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Твои жетоны образуют непрерывное соседство, связывающее два противоположных гекса вокруг одного тайла зарождения</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>СВОБОДНЫЙ БОЙ [free_action action=combat]</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>строка таблицы не найдена</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
+++ b/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
@@ -561,17 +561,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения</t>
+          <t>Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Оба примыкают к нестартовым тайлам зарождения</t>
+          <t>Оба примыкают к большим зарождениям</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Имей запитанными два своих добытчика, примыкающих к разным тайлам зарождения, — награда 6 монет и 1 трофей. Если оба примыкают к нестартовым тайлам зарождения, условие усилено: жетон модуля атаки. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
+          <t>Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям, — награда 3 монеты. Если оба примыкают к большим зарождениям, условие усилено: жетон модуля атаки. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения</t>
+          <t>В ЭТОТ ХОД забери последний келемий с зарождения</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Этим ты полностью исчерпал зарождение, и тайл ушёл с поля</t>
+          <t>ты исчерпал зарождение - оно ушло с поля</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД забери последний келемий с нестартового тайла зарождения — награда 6 монет и 1 трофей. Если ты этим полностью исчерпал зарождение и тайл ушёл с поля, условие усилено: жетон модуля сборки. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
+          <t>В ЭТОТ ХОД забери последний келемий с зарождения — награда 3 монеты. Если ты исчерпал зарождение и оно ушло с поля, условие усилено: жетон модуля сборки. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
         </is>
       </c>
     </row>
@@ -688,23 +688,23 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Обнули заодно и келемий</t>
+          <t>Не имей даже келемий</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4 монет, 1 трофей</t>
+          <t>2 монет, 1 БПР</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>1 трофей</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Имей одновременно ноль монет и ноль боеприпасов — награда 4 монеты и 1 трофей. Обнули заодно и келемий, и условие усилено: 2 трофея. Ва-банк играют только на голом столе.</t>
+          <t>Имей одновременно ноль монет и ноль боеприпасов — награда 2 монеты и 1 боеприпас. Не имей даже келемий, и условие усилено: 1 трофей. Ва-банк играют только на голом столе.</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД забери три контейнера — добытчиками или войсками</t>
+          <t>В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4 монет, 1 трофей</t>
+          <t>2 монет, 1 БПР</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД забери три контейнера — добытчиками или войсками, — награда 4 монеты и 1 трофей. Усиления у карты нет: три контейнера за ход и так работа всей смены. Каждый добытчик в Добыче выбирает одно: келемий или контейнер.</t>
+          <t>В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками) — награда 2 монеты и 1 боеприпас. Усиления у карты нет: три контейнера за ход и так работа всей смены. Каждый добытчик в Добыче выбирает одно: келемий или контейнер.</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Среди этих зданий есть и завод, и авиабаза</t>
+          <t>Эти здания - завод и авиабаза</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 монет, 1 карт задания</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД произведи только боеприпасы и ни одного войска — награда 1 трофей и 2 карты задания. Если среди этих зданий есть и завод, и авиабаза, условие усилено: 1 карта арсенала. Ход без единого нового войска — цена полного залпа.</t>
+          <t>В ЭТОТ ХОД произведи только боеприпасы и ни одного войска — награда 2 монеты и 1 карта задания. Если эти здания - завод и авиабаза, условие усилено: 1 карта арсенала. Ход без единого нового войска — цена полного залпа.</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Четыре войска, и все стоят на разных гексах</t>
+          <t>Четыре - и все стоят на разных гексах</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 монет, 1 карт задания</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Имей два своих войска на гексах, где нет твоих зданий, — награда 1 трофей и 2 карты задания. Если таких войск четыре и все стоят на разных гексах, условие усилено: жетон модуля сборки. Войско без своего здания рядом умрёт первым — зато не даром.</t>
+          <t>Имей два своих войска на гексах, где нет твоих зданий, — награда 2 монеты и 1 карта задания. Если таких войск четыре и все стоят на разных гексах, условие усилено: жетон модуля сборки. Войско без своего здания рядом умрёт первым — зато не даром.</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ</t>
+          <t>Имей на поле 2 свои вышки на разных гексах (обе не на гексе с ЦУ)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Хотя бы одна из этих вышек стоит на гексе, где есть жетоны противника</t>
+          <t>Одна из вышек стоит на гексе с жетонами врага</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>3 БПР</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Имей на поле две свои вышки на разных гексах, и ни одна из них не стоит на гексе с твоим ЦУ, — награда 6 боеприпасов и 1 трофей. Если хотя бы одна из этих вышек стоит на гексе, где есть жетоны противника, условие усилено: 4 трофея. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
+          <t>Имей на поле 2 свои вышки на разных гексах, и обе не на гексе с ЦУ, — награда 3 боеприпаса. Если одна из вышек стоит на гексе с жетонами врага, условие усилено: 2 трофея. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника</t>
+          <t>Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>3 БПР</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Имей своё войско внутри своего военного здания того же рода, стоящего на гексе, соседнем с гексом, где есть жетоны противника, — награда 6 боеприпасов и 1 трофей. Держи так сразу два войска, и условие усилено: 1 карта арсенала. Гарнизон в здании не виден до первого выстрела.</t>
+          <t>Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага, — награда 3 боеприпаса. Держи так сразу два войска, и условие усилено: 1 карта арсенала. Гарнизон в здании не виден до первого выстрела.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Имей своё войско на гексе, где стоит здание противника</t>
+          <t>Имей своё войско на гексе, где есть здания врага</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>3 БПР</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Имей своё войско на гексе, где стоит здание противника, — награда 6 боеприпасов и 1 трофей. Имей на одном таком гексе два своих войска, и условие усилено: 1 карта арсенала. Двор чужой, а гекс общий: здание закрывает только свои стенки, и войти во двор можно, пока в нём есть свободный сектор.</t>
+          <t>Имей своё войско на гексе, где есть здания врага, — награда 3 боеприпаса. Имей на одном таком гексе два своих войска, и условие усилено: 1 карта арсенала. Двор чужой, а гекс общий: здание закрывает только свои стенки, и войти во двор можно, пока в нём есть свободный сектор.</t>
         </is>
       </c>
     </row>
@@ -1110,22 +1110,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Имей в запасе ноль войск одного рода — весь род стоит на поле</t>
+          <t>Имей в запасе 0 войск одного вида</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Так стоят сразу два рода</t>
+          <t>Двух видов</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Имей в запасе ноль войск одного рода — весь род стоит на поле, — награда 1 трофей и 2 карты задания. Если так стоят сразу два рода, условие усилено: 4 трофея. Вывести род целиком значит подставить его целиком: в запасе не осталось никого, кем заменить убитого.</t>
+          <t>Имей в запасе 0 войск одного вида — награда 2 боеприпаса и 1 карта задания. Если так стоят сразу два рода, условие усилено: 2 трофея. Вывести род целиком значит подставить его целиком: в запасе не осталось никого, кем заменить убитого.</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД оплати три разных предложения на планшете рынка — напечатанные курсы и предложения карт сделок считаются по отдельности</t>
+          <t>В ЭТОТ ХОД воспользуйся двумя разными предложениями Рынка</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД оплати три разных предложения на планшете рынка — напечатанные курсы и предложения карт сделок считаются по отдельности. Награда: 6 монет и 1 трофей. Усиления у карты нет: печатных обменов на планшете осталось два, и три предложения набираются впритык — два печатных плюс одно с карты.</t>
+          <t>В ЭТОТ ХОД воспользуйся двумя разными предложениями Рынка. Награда: 3 монеты. Напечатанные курсы планшета и предложения карты рынка считаются по отдельности. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Дойди до второго шага хотя бы на одном треке технологий — награда 6 монет и 1 трофей. Стой на втором шаге сразу на двух треках, и условие усилено: 1 карта арсенала. Второй шаг — первое место, где трек начинает платить очками.</t>
+          <t>Дойди до второго шага хотя бы на одном треке технологий — награда 3 монеты. Стой на втором шаге сразу на двух треках, и условие усилено: 1 карта арсенала. Второй шаг — первое место, где трек начинает платить очками.</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением</t>
+          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4 монет, 1 трофей</t>
+          <t>1 монет, 2 БПР</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями планшета технологий — каждый трек и каждый вечный курс считаются отдельным предложением. Награда: 4 монеты и 1 трофей. Усиления у карты нет: на планшете науки три обмена, и три предложения — это ровно все они за один ход.</t>
+          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки. Награда: 1 монета и 2 боеприпаса. Шаг по треку и каждый обмен трофеев на планшете технологий считаются отдельным предложением; обменов на планшете три, значит три предложения — это ровно все они за один ход. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 4 карт задания</t>
+          <t>2 карт задания</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1375,7 +1375,7 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 1 трофей и 4 карты задания. На трёх треках условие усилено. Одно действие Науки двигает один трек, поэтому два трека — это два захода в науку за ход.</t>
+          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено. Одно действие Науки двигает один трек, поэтому два трека — это два захода в науку за ход.</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника, — награда 6 монет и 1 трофей. Если таких твоих зданий два и стоят они на разных гексах, условие усилено: 4 трофея. Подобраться стройкой к чужому штабу дороже, чем кажется: туда ещё надо дойти, и там по тебе будут бить.</t>
+          <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника, — награда 3 монеты. Если таких твоих зданий два и стоят они на разных гексах, условие усилено: 2 трофея. Подобраться стройкой к чужому штабу дороже, чем кажется: туда ещё надо дойти, и там по тебе будут бить.</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника</t>
+          <t>В ЭТОТ ХОД построй свое здание на гексе, соседнем с гексом, где есть войска врага</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй его на гексе, соседнем с гексом, где есть здание противника</t>
+          <t>На том же соседнем гексе есть здание врага</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда 6 монет и 1 трофей. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 карта арсенала. Передовая база строится под огнём — потому и платит.</t>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда 3 монеты. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 карта арсенала. Передовая база строится под огнём — потому и платит.</t>
         </is>
       </c>
     </row>
@@ -1537,17 +1537,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх</t>
+          <t>Все твои здания, требующие энергию, запитаны (не менее 3)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Доведи число зданий до четырёх, сохранив запитанность всех</t>
+          <t>Не менее 4 зданий</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Не имей на поле ни одного незапитанного здания, при этом зданий у тебя не меньше трёх, — награда 6 монет и 1 трофей. Доведи число зданий до четырёх, сохранив запитанность всех, и условие усилено: 1 карта арсенала. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
+          <t>Все твои здания, требующие энергию, запитаны, и таких зданий не менее трёх, — награда 3 монеты. Не менее четырёх зданий — условие усилено: 1 карта арсенала. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
         </is>
       </c>
     </row>
@@ -1608,18 +1608,18 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 монет, 1 карт задания</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>1 трофей</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД снеси своё здание и построй другое — награда 1 трофей и 2 карты задания. Если построенное встало на тот же гекс, где стояло снесённое, условие усилено: 2 трофея. Здание не переезжает: его сносят и ставят заново, и обе операции стоят действия.</t>
+          <t>В ЭТОТ ХОД снеси своё здание и построй другое — награда 2 монеты и 1 карта задания. Если построенное встало на тот же гекс, где стояло снесённое, условие усилено: 1 трофей. Здание не переезжает: его сносят и ставят заново, и обе операции стоят действия.</t>
         </is>
       </c>
     </row>
@@ -1659,22 +1659,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой</t>
+          <t>В ЭТОТ ХОД построй 2 здания на разных гексах</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Выполни три операции на трёх попарно несоседних гексах</t>
+          <t>3 здания на разных и несоседних между собой гексах</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>3 БПР</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>1 трофей</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД выполни две строительные операции на двух гексах, не соседних между собой, — награда 6 боеприпасов и 1 трофей. Выполни три операции на трёх попарно несоседних гексах, и условие усилено: 2 трофея. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
+          <t>В ЭТОТ ХОД построй 2 здания на разных гексах — награда 3 боеприпаса. Построй 3 здания на разных и несоседних между собой гексах, и условие усилено: 1 трофей. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
         </is>
       </c>
     </row>
@@ -1720,22 +1720,22 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника</t>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД на этом гексе два и более жетонов противника</t>
+          <t>На этом гексе два и более жетонов врага</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско противника, — награда 8 монет и 1 трофей. Если на этом гексе два и более жетонов противника, условие усилено: 4 трофея. Стройка под чужим стволом — заявка, а не расчёт.</t>
+          <t>В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага, — награда 4 монеты. Если на этом гексе два и более жетонов врага, условие усилено: 2 трофея. Стройка под чужим стволом — заявка, а не расчёт.</t>
         </is>
       </c>
     </row>
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух</t>
+          <t>Имей на двух зданиях - источниках энергии ровно один свободный кубик</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Держи так три источника</t>
+          <t>На трех источниках энергии</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Имей на каждом своём источнике энергии ровно один свободный кубик, и источников у тебя не меньше двух, — награда 8 монет и 1 трофей. Держи так три источника, и условие усилено: жетон модуля сборки. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному на каждом неудобно намеренно.</t>
+          <t>Имей на двух зданиях - источниках энергии ровно один свободный кубик — награда 4 монеты. На трёх источниках энергии условие усилено: жетон модуля сборки. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному неудобно намеренно.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>4 монет, 1 трофей</t>
+          <t>2 монет, 1 БПР</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>Сбрось карту арсенала — награда 4 монеты и 1 трофей. Сбрось вторую, и условие усилено: жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
+          <t>Сбрось карту арсенала — награда 2 монеты и 1 боеприпас. Сбрось вторую, и условие усилено: жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 монет, 1 карт задания</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Сдай в общий запас 2 боеприпаса — награда 1 трофей и 2 карты задания. Сдай пять, и условие усилено: карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
+          <t>Сдай в общий запас 2 боеприпаса — награда 2 монеты и 1 карта задания. Сдай пять, и условие усилено: карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Верни в свой запас два своих войска с поля</t>
+          <t>Верни в запас 2 своих войска с поля</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Это техника и/или авиация, и оба жетона с одного гекса</t>
+          <t>Технику и/или авиацию - и с одного гекса</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>6 БПР, 1 трофей</t>
+          <t>3 БПР</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Верни в свой запас два своих войска с поля — награда 6 боеприпасов и 1 трофей. Если это техника и/или авиация и оба жетона с одного гекса, условие усилено: жетон модуля сборки. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
+          <t>Верни в запас 2 своих войска с поля — награда 3 боеприпаса. Если это техника и/или авиация и оба жетона с одного гекса, условие усилено: жетон модуля сборки. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Сдай два своих неоткрытых контейнера — награда 6 монет и 1 трофей. Сдай четыре, и условие усилено: 4 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
+          <t>Сдай два своих неоткрытых контейнера — награда 3 монеты. Сдай четыре, и условие усилено: 2 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
         </is>
       </c>
     </row>
@@ -2102,17 +2102,17 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь технику или авиацию противника</t>
+          <t>В ЭТОТ ХОД уничтожь технику или авиацию врага</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>И ещё два любых чужих жетона</t>
+          <t>и еще 2 жетона любого врага</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь технику или авиацию противника — награда 8 монет и 1 трофей. Если снял ещё два любых чужих жетона, условие усилено: карта арсенала. Техника и авиация дороже прочего и стоят дальше от чужих стен: до них ещё надо дотянуться.</t>
+          <t>В ЭТОТ ХОД уничтожь технику или авиацию врага — награда 4 монеты. Если снял ещё два любых чужих жетона, условие усилено: карта арсенала. Техника и авиация дороже прочего и стоят дальше от чужих стен: до них ещё надо дотянуться.</t>
         </is>
       </c>
     </row>
@@ -2163,17 +2163,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь все жетоны противника на одном гексе</t>
+          <t>В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Их на этом гексе было не меньше трёх</t>
+          <t>их на этом гексе не менее 3</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь все жетоны противника на одном гексе — награда 8 монет и 1 трофей. Если их там было не меньше трёх, условие усилено: жетон модуля атаки. Вычистить гекс целиком — работа не одного выстрела: здание закрывает гекс, и снимать приходится по очереди.</t>
+          <t>В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе — награда 4 монеты. Если их там было не меньше трёх, условие усилено: жетон модуля атаки. Вычистить гекс целиком — работа не одного выстрела: здание закрывает гекс, и снимать приходится по очереди.</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД этот добытчик был полностью запитан и примыкал к келемию</t>
+          <t>Этот добытчик был полностью запитан и примыкал к келемию</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь добытчик противника — награда 8 монет и 1 трофей. Если этот добытчик был полностью запитан и примыкал к келемию, условие усилено: жетон модуля атаки. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи — а работающий на полную вдвое дороже.</t>
+          <t>В ЭТОТ ХОД уничтожь добытчик противника — награда 4 монеты. Если этот добытчик был полностью запитан и примыкал к келемию, условие усилено: жетон модуля атаки. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи — а работающий на полную вдвое дороже.</t>
         </is>
       </c>
     </row>
@@ -2285,17 +2285,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетон противника</t>
+          <t>Имей среди уничтоженных жетонов жетон врага</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Их два, и один из них — добытчик</t>
+          <t>два жетона, один из них - добытчик</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетон противника — награда 8 монет и 1 трофей. Если их два и один из них добытчик, условие усилено: жетон модуля атаки. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
+          <t>Имей среди уничтоженных жетонов жетон врага — награда 4 монеты. Если их два и один из них добытчик, условие усилено: жетон модуля атаки. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов два жетона противника</t>
+          <t>Имей среди уничтоженных жетонов два жетона врага</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов два жетона противника — награда 8 монет и 1 трофей. Если один из них энергостанция, условие усилено: жетон модуля сборки. Энергостанция питает всё остальное, поэтому её снос стоит противнику дороже собственной цены.</t>
+          <t>Имей среди уничтоженных жетонов два жетона врага — награда 4 монеты. Если один из них энергостанция, условие усилено: жетон модуля сборки. Энергостанция питает всё остальное, поэтому её снос стоит противнику дороже собственной цены.</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетоны двух разных противников — награда 8 монет и 1 трофей. Если оба этих жетона здания, условие усилено: жетон модуля сборки. Единственная карта колоды, которую нельзя закрыть, воюя с одним соседом.</t>
+          <t>Имей среди уничтоженных жетонов жетоны двух разных противников — награда 4 монеты. Если оба этих жетона здания, условие усилено: жетон модуля сборки. Единственная карта колоды, которую нельзя закрыть, воюя с одним соседом.</t>
         </is>
       </c>
     </row>
@@ -2473,17 +2473,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Уничтоженный жетон был техникой или авиацией</t>
+          <t>В ЭТОТ ХОД уничтоженный жетон был техникой или авиацией</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 монет, 1 карт задания</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>1 трофей</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя, — награда 1 трофей и 2 карты задания. Если уничтоженный был техникой или авиацией, условие усилено: 2 трофея. Бить сильнейшего значит получить сдачи, и карта платит именно за это.</t>
+          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя, — награда 2 монеты и 1 карта задания. Если уничтоженный был техникой или авиацией, условие усилено: 1 трофей. Бить сильнейшего значит получить сдачи, и карта платит именно за это.</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8 монет, 1 трофей</t>
+          <t>4 монет</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь два жетона противника — награда 8 монет и 1 трофей. Если у одного из них прочность была 2 или больше, условие усилено: жетон модуля атаки. Первая кровь считается по двум, а не по одному.</t>
+          <t>В ЭТОТ ХОД уничтожь два жетона противника — награда 4 монеты. Если у одного из них прочность была 2 или больше, условие усилено: жетон модуля атаки. Первая кровь считается по двум, а не по одному.</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>1 трофей</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда 1 трофей и 2 карты задания. Если уничтоженный жетон был зданием, условие усилено: 2 трофея. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
+          <t>В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда 2 боеприпаса и 1 карта задания. Если уничтоженный жетон был зданием, условие усилено: 1 трофей. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
         </is>
       </c>
     </row>
@@ -2656,17 +2656,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Это была энергостанция третьего или четвёртого уровня</t>
+          <t>Это была энергостанция 3 или 4 уровня.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД уничтожь энергостанцию противника — награда 1 трофей и 2 карты задания. Если это была энергостанция третьего или четвёртого уровня, условие усилено: 4 трофея. Крупные энергостанции стоят в глубине, и лезть за ними опасно.</t>
+          <t>В ЭТОТ ХОД уничтожь энергостанцию противника — награда 2 боеприпаса и 1 карта задания. Если это была энергостанция третьего или четвёртого уровня, условие усилено: 2 трофея. Крупные энергостанции стоят в глубине, и лезть за ними опасно.</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Имей на поле все свои энергостанции</t>
+          <t>Имей на поле все свои 4 здания энергостанций</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 4 карт задания</t>
+          <t>2 карт задания</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Имей на поле все свои энергостанции — награда 1 трофей и 4 карты задания. Полный комплект источников на поле — лучшая мишень в партии: их нечем прикрыть и негде спрятать.</t>
+          <t>Имей на поле все свои 4 здания энергостанций — награда 2 карты задания. Полный комплект источников на поле — лучшая мишень в партии: их нечем прикрыть и негде спрятать.</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Имей на поле все свои добытчики</t>
+          <t>Имей на поле все свои 4 здания добытчиков</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1 трофей, 4 карт задания</t>
+          <t>2 карт задания</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Имей на поле все свои добытчики — награда 1 трофей и 4 карты задания. Разложил всё, чем добываешь, — держи оборону или жги карту: у добытчика прочность один.</t>
+          <t>Имей на поле все свои 4 здания добытчиков — награда 2 карты задания. Разложил всё, чем добываешь, — держи оборону или жги карту: у добытчика прочность один.</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 монет, 1 карт задания</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД найми два войска разных родов — награда 1 трофей и 2 карты задания. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 4 трофея. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
+          <t>В ЭТОТ ХОД найми два войска разных родов — награда 2 монеты и 1 карта задания. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 2 трофея. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
         </is>
       </c>
     </row>
@@ -2895,22 +2895,22 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Займи войсками четыре разных гекса, и родов среди них не меньше двух</t>
+          <t>Займи 4 разных гекса войсками хотя бы 2 видов</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Шесть гексов</t>
+          <t>6 гексов</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6 монет, 1 трофей</t>
+          <t>3 монет</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4 трофей</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Займи войсками четыре разных гекса, и родов среди них не меньше двух, — награда 6 монет и 1 трофей. Шесть гексов, и условие усилено: 4 трофея. Растянуться по полю выгодно и опасно разом: где тонко, там и порвут.</t>
+          <t>Займи 4 разных гекса войсками хотя бы 2 видов — награда 3 монеты. 6 гексов, и условие усилено: 2 трофея. Растянуться по полю выгодно и опасно разом: где тонко, там и порвут.</t>
         </is>
       </c>
     </row>
@@ -2956,17 +2956,17 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Займи войсками пять разных гексов</t>
+          <t>Займи войсками 5 разных гексов</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>На двух из них есть здания противника</t>
+          <t>На 2 из них есть здания противника</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1 трофей, 2 карт задания</t>
+          <t>2 БПР, 1 карт задания</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>Займи войсками пять разных гексов — награда 1 трофей и 2 карты задания. Если на двух из них есть здания противника, условие усилено: 1 карта арсенала. Гекс с чужим зданием закрыт: стоять там можно, бить оттуда — только по зданиям и вышкам.</t>
+          <t>Займи войсками 5 разных гексов — награда 2 боеприпаса и 1 карта задания. Если на двух из них есть здания противника, условие усилено: 1 карта арсенала. Гекс с чужим зданием закрыт: стоять там можно, бить оттуда — только по зданиям и вышкам.</t>
         </is>
       </c>
     </row>

--- a/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
+++ b/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
@@ -1192,7 +1192,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain ammo=1 order=operation]</t>
+          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain order=operation ammo=1]</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain ammo=1 order=operation]</t>
+          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain order=operation ammo=1]</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2 монет, 1 БПР</t>
+          <t>2 монет, 1 БПР, attack модуль</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>attack модуль</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>Сбрось карту арсенала — награда 2 монеты и 1 боеприпас. Сбрось вторую, и условие усилено: жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
+          <t>Сбрось карту арсенала — награда 2 монеты и 1 боеприпас и жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2 монет, 1 карт задания</t>
+          <t>2 монет, 1 карт задания, 1 карта арсенала</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1 карта арсенала</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Сдай в общий запас 2 боеприпаса — награда 2 монеты и 1 карта задания. Сдай пять, и условие усилено: карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
+          <t>Сдай в общий запас 2 боеприпаса — награда 2 монеты и 1 карта задания и 1 карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3 монет</t>
+          <t>3 монет, 2 трофей</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain ammo=1 order=operation]</t>
+          <t>+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ [gain order=operation ammo=1]</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Сдай два своих неоткрытых контейнера — награда 3 монеты. Сдай четыре, и условие усилено: 2 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
+          <t>Сдай два своих неоткрытых контейнера — награда 3 монеты и 2 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
         </is>
       </c>
     </row>

--- a/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
+++ b/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
@@ -704,7 +704,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1369,13 +1369,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 трофей</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено. Одно действие Науки двигает один трек, поэтому два трека — это два захода в науку за ход.</t>
+          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено: 2 трофея. Одно действие Науки берёт сколько угодно разных треков, по шагу на каждом, — но каждый шаг оплачивается трофеями отдельно.</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action action=combat attack_tokens=1]</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ [free_action attack_tokens=1 action=combat]</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">

--- a/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
+++ b/docs/ЗАДАНИЯ — все карты (обычные, начальные, супер).xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2 трофей</t>
+          <t>1 карта арсенала</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено: 2 трофея. Одно действие Науки берёт сколько угодно разных треков, по шагу на каждом, — но каждый шаг оплачивается трофеями отдельно.</t>
+          <t>В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено: 1 карта арсенала. Одно действие Науки берёт сколько угодно разных треков, по шагу на каждом, — но каждый шаг оплачивается трофеями отдельно.</t>
         </is>
       </c>
     </row>
